--- a/results/job_matches_2026-10-06.xlsx
+++ b/results/job_matches_2026-10-06.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,25 +631,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect-4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Medallion Architecture</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,24 +659,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3d45a3054cc31c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad2431edc28d94e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer, Data - FreeWheel</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Medallion Architecture</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad2431edc28d94e</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb9c7f9097d165</t>
         </is>
       </c>
     </row>
@@ -841,95 +841,95 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Meetic</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7952341ee0c6ac4</t>
+          <t>https://www.indeed.com/viewjob?jk=3904d0205e58da2c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Data Analyst - Agentic AI</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819ad471f98483cc</t>
+          <t>https://www.indeed.com/viewjob?jk=04b6ea3bc33b1453</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Meetic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f0317152441f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7952341ee0c6ac4</t>
         </is>
       </c>
     </row>
@@ -960,11 +960,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b1fb40eeb66f17</t>
+          <t>https://www.indeed.com/viewjob?jk=819ad471f98483cc</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -999,34 +999,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b016308efc3eae2</t>
+          <t>https://www.indeed.com/viewjob?jk=956de72fea7773ed</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=299b4bbe67f91792</t>
+          <t>https://www.indeed.com/viewjob?jk=21f0317152441f3f</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a78c8e54c1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=9b016308efc3eae2</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15dd7b9cef5a234</t>
+          <t>https://www.indeed.com/viewjob?jk=299b4bbe67f91792</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2691989b708f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a78c8e54c1f97</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd44e886a3ff4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a15dd7b9cef5a234</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7013b6133945b032</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2691989b708f3</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0da7fcfc987a7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd44e886a3ff4ba</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600e123842bacfc7</t>
+          <t>https://www.indeed.com/viewjob?jk=7013b6133945b032</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Product Engineer, Karat Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,32 +1324,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4503e534007dd850</t>
+          <t>https://www.indeed.com/viewjob?jk=a0da7fcfc987a7ea</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEI Consultants</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5425f278842298</t>
+          <t>https://www.indeed.com/viewjob?jk=600e123842bacfc7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solutions Architect (Contract)</t>
+          <t>Product Engineer, Karat Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sound Physicians</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Dataflow, Scala, Snowflake, Data Modeling, Power BI</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,32 +1394,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca6d8b53f7fae1d</t>
+          <t>https://www.indeed.com/viewjob?jk=4503e534007dd850</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>AI Data Analyst - Agentic AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Integrated Financial Settlements</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Kafka</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,24 +1429,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870e38fac0b2d478</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b1fb40eeb66f17</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Managing Engineer, Software Engineering -Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb172bb48712256</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5425f278842298</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Solutions Architect (Contract)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>Sound Physicians</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,42 +1489,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Step Functions, SQS, SNS, BigQuery, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Dataflow, Scala, Snowflake, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1d738eb2126f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca6d8b53f7fae1d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Integrated Financial Settlements</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,42 +1534,42 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5b52e17a5bd63e</t>
+          <t>https://www.indeed.com/viewjob?jk=870e38fac0b2d478</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer-3</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, Step Functions, SQS, SNS, BigQuery, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33bb747e2908314c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1d738eb2126f6c</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>iClassPro, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1594,34 +1594,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=579a554b68cd573e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f5b52e17a5bd63e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. People Analytics Engineer</t>
+          <t>Data Engineer-3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,34 +1629,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92e55014f77298b</t>
+          <t>https://www.indeed.com/viewjob?jk=33bb747e2908314c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Palomar College</t>
+          <t>iClassPro, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Scala, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5c414e4ee4b328</t>
+          <t>https://www.indeed.com/viewjob?jk=579a554b68cd573e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Sr. People Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Triconn Solutions</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,24 +1699,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=985b7795e94b06ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b92e55014f77298b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Back-End Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arecibo, PR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,42 +1734,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f552257cba93bb49</t>
+          <t>https://www.indeed.com/viewjob?jk=d422fc46951e5afd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Qbitech</t>
+          <t>Palomar College</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,32 +1779,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea14e8ca5424e9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5c414e4ee4b328</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Triconn Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, ETL</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,32 +1814,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b788dde189e4cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=985b7795e94b06ce</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arecibo, PR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099479d86490847b</t>
+          <t>https://www.indeed.com/viewjob?jk=f552257cba93bb49</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Reliability Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Qbitech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,24 +1884,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6dc0fbf3996a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea14e8ca5424e9cb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Reliability Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,24 +1919,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708e5d96e2689486</t>
+          <t>https://www.indeed.com/viewjob?jk=0b788dde189e4cc1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,24 +1954,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53183509479236f6</t>
+          <t>https://www.indeed.com/viewjob?jk=099479d86490847b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Sr. Data Reliability Engineer I</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,24 +1989,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9468ea1e9b04ea28</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6dc0fbf3996a4c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Reliability Engineer I</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rooms To Go</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seffner, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,34 +2014,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f34931ade8cede</t>
+          <t>https://www.indeed.com/viewjob?jk=708e5d96e2689486</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e21d24f6967c76</t>
+          <t>https://www.indeed.com/viewjob?jk=9468ea1e9b04ea28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer, Advanced Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Rooms To Go</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seffner, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,462 +2084,462 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ef5d52f3729890</t>
+          <t>https://www.indeed.com/viewjob?jk=86f34931ade8cede</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Solace Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, dbt, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164a7939c0934d10</t>
+          <t>https://www.indeed.com/viewjob?jk=8db24154655e7b30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb80f8127789b70</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0306b9c06d1ef3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Advanced Software Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Vertex AI, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbab632d0bb04999</t>
+          <t>https://www.indeed.com/viewjob?jk=02f1ae8db3b512b9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f029f2695a0348</t>
+          <t>https://www.indeed.com/viewjob?jk=22b0f3b9859f414e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2532cb430ae39af4</t>
+          <t>https://www.indeed.com/viewjob?jk=86a9ba9a98dcb9b2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb45b4747cbece</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd6f7ce6a7a901</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d991735fb9948be</t>
+          <t>https://www.indeed.com/viewjob?jk=87f1b7beb2c6b9c0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3966f55aaa1e266e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb96a18f22d94cfc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710806077ea87813</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9109c01437b799</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe90612a7cd40771</t>
+          <t>https://www.indeed.com/viewjob?jk=0aef30d45a8f939e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653ba6f45e27b32b</t>
+          <t>https://www.indeed.com/viewjob?jk=61392ca76495c8ad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=498781f26e16eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc5809be7fcc0f3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ede594b070d17f3</t>
+          <t>https://www.indeed.com/viewjob?jk=74e21d24f6967c76</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Advanced Analytics</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42ea61bfb332a47</t>
+          <t>https://www.indeed.com/viewjob?jk=44ef5d52f3729890</t>
         </is>
       </c>
     </row>
@@ -2596,20 +2596,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Allied Benefit Systems</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c44231ffe29ae48</t>
+          <t>https://www.indeed.com/viewjob?jk=2168430383941cce</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Solace Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Converse, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, dbt, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadd1c9e9b39a370</t>
+          <t>https://www.indeed.com/viewjob?jk=164a7939c0934d10</t>
         </is>
       </c>
     </row>
@@ -2666,20 +2666,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb72e2bc4fddaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb80f8127789b70</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Senior Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Azure, Databricks, GCP, Vertex AI, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ff7692093a84ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fbab632d0bb04999</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer (R0172063) - (SSFB/HSV) (2 Positions)</t>
+          <t>Data Modeler/Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>INNOVIM DEFENSE SERVICES, LLC</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2759,67 +2759,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b39435d6c83f900a</t>
+          <t>https://www.indeed.com/viewjob?jk=065b398cf1864aa5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wilson Language Training Corp.</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=206b79ebbffc09e0</t>
+          <t>https://www.indeed.com/viewjob?jk=94f029f2695a0348</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Consultant, Full Stack API Developer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2829,32 +2829,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=769605ecbc4da595</t>
+          <t>https://www.indeed.com/viewjob?jk=2532cb430ae39af4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer (NJUS)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NetJets</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, ECS, Scala, Kafka, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2864,32 +2864,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89f3336b4c40b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb45b4747cbece</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Senior</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2899,32 +2899,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2748f5c3e0997c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d991735fb9948be</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Senior</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2934,32 +2934,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b748bf2b91e4a02e</t>
+          <t>https://www.indeed.com/viewjob?jk=3966f55aaa1e266e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Automation Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2969,32 +2969,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33a4e4327114b742</t>
+          <t>https://www.indeed.com/viewjob?jk=710806077ea87813</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Engineer (1042) – Department of Technology</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3004,32 +3004,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe04b5d2de255308</t>
+          <t>https://www.indeed.com/viewjob?jk=fe90612a7cd40771</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3039,32 +3039,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35e334b90160652</t>
+          <t>https://www.indeed.com/viewjob?jk=653ba6f45e27b32b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AEP Middleware Pod Kafka Admin</t>
+          <t>Full-stack Engineer 4 - Card Tech</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Kafka Connect, Snowflake, Oracle, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3074,42 +3074,1022 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c7915433a059ea</t>
+          <t>https://www.indeed.com/viewjob?jk=854d296ae3e1537f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=498781f26e16eb5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Roswell, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ede594b070d17f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f42ea61bfb332a47</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c44231ffe29ae48</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Converse, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fadd1c9e9b39a370</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb72e2bc4fddaba5</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Platform Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Redwood Logistics</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9ff7692093a84ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DevSecOps Engineer (R0172063) - (SSFB/HSV) (2 Positions)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>INNOVIM DEFENSE SERVICES, LLC</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b39435d6c83f900a</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Wilson Language Training Corp.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=206b79ebbffc09e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Consultant, Full Stack API Developer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Infinitive Inc</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=769605ecbc4da595</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4, Cyber Endpoint Security</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=768daf548bf7f04f</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=727d755000763cf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4 (ServiceNow)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abe17e114c2bcc25</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=239112321618bfea</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 (Java, Python, AWS)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f20993d5ae69d49</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77827d49349dcffa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d562816e08aec62b</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AI Software Engineer - Senior</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2748f5c3e0997c3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AI Software Engineer - Senior</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b748bf2b91e4a02e</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Quality Assurance Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Federal Reserve Bank of St. Louis</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, Python</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33a4e4327114b742</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (1042) – Department of Technology</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>City and County of San Francisco</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe04b5d2de255308</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Sr Engineer, Applications - LATAM</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Shoals Technologies Group</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Portland, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82cde14623807d01</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Shoals Technologies Group</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Portland, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=821c9233233a720b</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Java Application Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a35e334b90160652</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer - Angular Focus</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Imperial Health Holdings</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca22063859741953</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>Business Intelligence (BI) Developer</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>ICF</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Reston, VA, US USA</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D102" t="n">
         <v>10.4</v>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=26c52bf7b46f0d46</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AEP Middleware Pod Kafka Admin</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, Kafka Connect, Snowflake, Oracle, Splunk, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7c7915433a059ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f9f54f4c0964669</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DevOps Engineer III</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Victra-Verizon Authorized Retailer</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bbd1ecd34ba576b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-06.xlsx
+++ b/results/job_matches_2026-10-06.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Management &amp; BI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52dec15d92eb10</t>
+          <t>https://www.indeed.com/viewjob?jk=71bf0245152c804d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer / BI Developer – GCP, dbt &amp; Power BI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>OSI Digital</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71bf0245152c804d</t>
+          <t>https://www.indeed.com/viewjob?jk=79eb3256392d49d1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer III AI, Automation, &amp; Data Engineering</t>
+          <t>Site Reliability Engineer, Data - FreeWheel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b965769d33666ec</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb9c7f9097d165</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer / BI Developer – GCP, dbt &amp; Power BI</t>
+          <t>Commercial DT Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OSI Digital</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79eb3256392d49d1</t>
+          <t>https://www.indeed.com/viewjob?jk=eec85fd3b937ce66</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Managing Engineer, Data Engineering</t>
+          <t>Sr. AI Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Scala, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,67 +624,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f0324e9bc372ed</t>
+          <t>https://www.indeed.com/viewjob?jk=422f525072d1a9c4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Medallion Architecture</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad2431edc28d94e</t>
+          <t>https://www.indeed.com/viewjob?jk=3904d0205e58da2c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Data - FreeWheel</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Lindfast Solutions Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb9c7f9097d165</t>
+          <t>https://www.indeed.com/viewjob?jk=981d541cfbb05547</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Commercial DT Senior Data Solution Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Meetic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,67 +729,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec85fd3b937ce66</t>
+          <t>https://www.indeed.com/viewjob?jk=c7952341ee0c6ac4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c956f1cdfac97bda</t>
+          <t>https://www.indeed.com/viewjob?jk=271ae7d8ee6706bd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Analyst / Analytics Developer</t>
+          <t>AI Data Analyst - Agentic AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VASERJOB</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,137 +799,137 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bc1ca87aba01e9</t>
+          <t>https://www.indeed.com/viewjob?jk=819ad471f98483cc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. AI Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Scala, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422f525072d1a9c4</t>
+          <t>https://www.indeed.com/viewjob?jk=956de72fea7773ed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3904d0205e58da2c</t>
+          <t>https://www.indeed.com/viewjob?jk=21f0317152441f3f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Product Engineer, Karat Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04b6ea3bc33b1453</t>
+          <t>https://www.indeed.com/viewjob?jk=4503e534007dd850</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Meetic</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,102 +939,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7952341ee0c6ac4</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5425f278842298</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Data Analyst - Agentic AI</t>
+          <t>Data Engineer – Physical AI Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819ad471f98483cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a8048f9d73fd7da7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle</t>
+          <t>AWS, Redshift, Step Functions, SQS, SNS, BigQuery, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956de72fea7773ed</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1d738eb2126f6c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Integrated Financial Settlements</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f0317152441f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=870e38fac0b2d478</t>
         </is>
       </c>
     </row>
@@ -1056,20 +1056,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b016308efc3eae2</t>
+          <t>https://www.indeed.com/viewjob?jk=0f5b52e17a5bd63e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=299b4bbe67f91792</t>
+          <t>https://www.indeed.com/viewjob?jk=33bb747e2908314c</t>
         </is>
       </c>
     </row>
@@ -1126,42 +1126,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>iClassPro, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a78c8e54c1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=579a554b68cd573e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. People Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1170,46 +1170,46 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15dd7b9cef5a234</t>
+          <t>https://www.indeed.com/viewjob?jk=b92e55014f77298b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Palomar College</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2691989b708f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0b5c414e4ee4b328</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Triconn Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,42 +1254,42 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd44e886a3ff4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=985b7795e94b06ce</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Back-End Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7013b6133945b032</t>
+          <t>https://www.indeed.com/viewjob?jk=d422fc46951e5afd</t>
         </is>
       </c>
     </row>
@@ -1301,20 +1301,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Qbitech</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0da7fcfc987a7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ea14e8ca5424e9cb</t>
         </is>
       </c>
     </row>
@@ -1336,20 +1336,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600e123842bacfc7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b788dde189e4cc1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Product Engineer, Karat Platform</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,32 +1394,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4503e534007dd850</t>
+          <t>https://www.indeed.com/viewjob?jk=099479d86490847b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Data Analyst - Agentic AI</t>
+          <t>Sr. Data Reliability Engineer I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,32 +1429,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b1fb40eeb66f17</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6dc0fbf3996a4c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Reliability Engineer I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,54 +1464,54 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5425f278842298</t>
+          <t>https://www.indeed.com/viewjob?jk=708e5d96e2689486</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solutions Architect (Contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sound Physicians</t>
+          <t>Rooms To Go</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seffner, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Dataflow, Scala, Snowflake, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca6d8b53f7fae1d</t>
+          <t>https://www.indeed.com/viewjob?jk=86f34931ade8cede</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Integrated Financial Settlements</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1520,11 +1520,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,339 +1534,339 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870e38fac0b2d478</t>
+          <t>https://www.indeed.com/viewjob?jk=74e21d24f6967c76</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer – Backend</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Step Functions, SQS, SNS, BigQuery, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1d738eb2126f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff1e374638f96eca</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5b52e17a5bd63e</t>
+          <t>https://www.indeed.com/viewjob?jk=8db24154655e7b30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer-3</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33bb747e2908314c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0306b9c06d1ef3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>iClassPro, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, ETL, ELT, dbt</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=579a554b68cd573e</t>
+          <t>https://www.indeed.com/viewjob?jk=02f1ae8db3b512b9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. People Analytics Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92e55014f77298b</t>
+          <t>https://www.indeed.com/viewjob?jk=22b0f3b9859f414e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Back-End Developer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d422fc46951e5afd</t>
+          <t>https://www.indeed.com/viewjob?jk=86a9ba9a98dcb9b2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Palomar College</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Scala, SQL Server</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5c414e4ee4b328</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd6f7ce6a7a901</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Triconn Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=985b7795e94b06ce</t>
+          <t>https://www.indeed.com/viewjob?jk=87f1b7beb2c6b9c0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arecibo, PR, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f552257cba93bb49</t>
+          <t>https://www.indeed.com/viewjob?jk=bb96a18f22d94cfc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Qbitech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,34 +1874,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea14e8ca5424e9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9109c01437b799</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,34 +1909,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, ETL</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b788dde189e4cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=0aef30d45a8f939e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Software Engineer, Advanced Analytics</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,67 +1954,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099479d86490847b</t>
+          <t>https://www.indeed.com/viewjob?jk=44ef5d52f3729890</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Reliability Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, RDS, Spark, PySpark, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6dc0fbf3996a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c126f4e3cc33b7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Reliability Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Allied Benefit Systems</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,19 +2024,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708e5d96e2689486</t>
+          <t>https://www.indeed.com/viewjob?jk=2168430383941cce</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Solace Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2045,11 +2045,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, dbt, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9468ea1e9b04ea28</t>
+          <t>https://www.indeed.com/viewjob?jk=164a7939c0934d10</t>
         </is>
       </c>
     </row>
@@ -2071,300 +2071,300 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rooms To Go</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seffner, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f34931ade8cede</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb80f8127789b70</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Data Modeler/Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db24154655e7b30</t>
+          <t>https://www.indeed.com/viewjob?jk=065b398cf1864aa5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0306b9c06d1ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=94f029f2695a0348</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f1ae8db3b512b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2532cb430ae39af4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b0f3b9859f414e</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb45b4747cbece</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a9ba9a98dcb9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6d991735fb9948be</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd6f7ce6a7a901</t>
+          <t>https://www.indeed.com/viewjob?jk=3966f55aaa1e266e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87f1b7beb2c6b9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=710806077ea87813</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Workday Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Yitro Global</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,172 +2374,172 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb96a18f22d94cfc</t>
+          <t>https://www.indeed.com/viewjob?jk=5f01cb6ed116418a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Senior Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Azure, Databricks, GCP, Vertex AI, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9109c01437b799</t>
+          <t>https://www.indeed.com/viewjob?jk=fbab632d0bb04999</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aef30d45a8f939e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe90612a7cd40771</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61392ca76495c8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=653ba6f45e27b32b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>Full-stack Engineer 4 - Card Tech</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc5809be7fcc0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=854d296ae3e1537f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e21d24f6967c76</t>
+          <t>https://www.indeed.com/viewjob?jk=498781f26e16eb5d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer, Advanced Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL, Data Modeling, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ef5d52f3729890</t>
+          <t>https://www.indeed.com/viewjob?jk=8ede594b070d17f3</t>
         </is>
       </c>
     </row>
@@ -2596,20 +2596,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Allied Benefit Systems</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, MLOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2168430383941cce</t>
+          <t>https://www.indeed.com/viewjob?jk=f42ea61bfb332a47</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Solace Health</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, dbt, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164a7939c0934d10</t>
+          <t>https://www.indeed.com/viewjob?jk=4c44231ffe29ae48</t>
         </is>
       </c>
     </row>
@@ -2666,20 +2666,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Converse, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb80f8127789b70</t>
+          <t>https://www.indeed.com/viewjob?jk=fadd1c9e9b39a370</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Advanced Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Vertex AI, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbab632d0bb04999</t>
+          <t>https://www.indeed.com/viewjob?jk=cb72e2bc4fddaba5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Modeler/Architect</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2759,102 +2759,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=065b398cf1864aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ff7692093a84ad</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Wilson Language Training Corp.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f029f2695a0348</t>
+          <t>https://www.indeed.com/viewjob?jk=206b79ebbffc09e0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Erwin Data Modeler</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Tekcogno</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Hadoop, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2532cb430ae39af4</t>
+          <t>https://www.indeed.com/viewjob?jk=89810a7e8484847e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Consultant, Full Stack API Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2864,67 +2864,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb45b4747cbece</t>
+          <t>https://www.indeed.com/viewjob?jk=769605ecbc4da595</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer - Digital Marketing</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Live Oak Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d991735fb9948be</t>
+          <t>https://www.indeed.com/viewjob?jk=4a3a03e231e77efd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Full-stack Engineer 4, Cyber Endpoint Security</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2934,32 +2934,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3966f55aaa1e266e</t>
+          <t>https://www.indeed.com/viewjob?jk=768daf548bf7f04f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2969,32 +2969,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710806077ea87813</t>
+          <t>https://www.indeed.com/viewjob?jk=727d755000763cf2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Full Stack Engineer 4 (ServiceNow)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3004,32 +3004,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe90612a7cd40771</t>
+          <t>https://www.indeed.com/viewjob?jk=abe17e114c2bcc25</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3039,14 +3039,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653ba6f45e27b32b</t>
+          <t>https://www.indeed.com/viewjob?jk=239112321618bfea</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Card Tech</t>
+          <t>Full-Stack Engineer 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854d296ae3e1537f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f20993d5ae69d49</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3109,24 +3109,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=498781f26e16eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=77827d49349dcffa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-Stack Engineer 4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3144,32 +3144,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ede594b070d17f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d562816e08aec62b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Software Engineer - Senior</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3179,32 +3179,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42ea61bfb332a47</t>
+          <t>https://www.indeed.com/viewjob?jk=2748f5c3e0997c3f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Software Engineer - Senior</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3214,32 +3214,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c44231ffe29ae48</t>
+          <t>https://www.indeed.com/viewjob?jk=b748bf2b91e4a02e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Quality Assurance Automation Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Federal Reserve Bank of St. Louis</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Converse, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3249,67 +3249,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadd1c9e9b39a370</t>
+          <t>https://www.indeed.com/viewjob?jk=33a4e4327114b742</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>bet365</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb72e2bc4fddaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=e156aa015e45d8c1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Cloud Engineer (1042) – Department of Technology</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3319,32 +3319,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ff7692093a84ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fe04b5d2de255308</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer (R0172063) - (SSFB/HSV) (2 Positions)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>INNOVIM DEFENSE SERVICES, LLC</t>
+          <t>Shoals Technologies Group</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Portland, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3354,19 +3354,19 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b39435d6c83f900a</t>
+          <t>https://www.indeed.com/viewjob?jk=821c9233233a720b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Wilson Language Training Corp.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3375,151 +3375,151 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=206b79ebbffc09e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a35e334b90160652</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Consultant, Full Stack API Developer</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=769605ecbc4da595</t>
+          <t>https://www.indeed.com/viewjob?jk=6372ad68f53bdf20</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Cyber Endpoint Security</t>
+          <t>Backend Software Engineer, Weather &amp; Aviation</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Spire Global</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Kafka, Dask</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=768daf548bf7f04f</t>
+          <t>https://www.indeed.com/viewjob?jk=b20f49a9fd1e357a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Backend Software Engineer, Weather &amp; Aviation</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>spire</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Kafka, Dask</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727d755000763cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=1555a6e30192df1d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (ServiceNow)</t>
+          <t>AEP Middleware Pod Kafka Admin</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Kafka, Kafka Connect, Snowflake, Oracle, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3529,67 +3529,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe17e114c2bcc25</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c7915433a059ea</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Developer - Angular Focus</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Imperial Health Holdings</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239112321618bfea</t>
+          <t>https://www.indeed.com/viewjob?jk=ca22063859741953</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Python, AWS)</t>
+          <t>Business Intelligence (BI) Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3599,67 +3599,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f20993d5ae69d49</t>
+          <t>https://www.indeed.com/viewjob?jk=26c52bf7b46f0d46</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77827d49349dcffa</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9f54f4c0964669</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Victra-Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3668,426 +3668,6 @@
         </is>
       </c>
       <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d562816e08aec62b</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>AI Software Engineer - Senior</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Cupertino, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2748f5c3e0997c3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>AI Software Engineer - Senior</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Cupertino, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b748bf2b91e4a02e</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Quality Assurance Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Federal Reserve Bank of St. Louis</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, Python</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33a4e4327114b742</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Cloud Engineer (1042) – Department of Technology</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>City and County of San Francisco</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe04b5d2de255308</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Sr Engineer, Applications - LATAM</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Shoals Technologies Group</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Portland, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82cde14623807d01</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Shoals Technologies Group</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Portland, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=821c9233233a720b</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Java Application Architect</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a35e334b90160652</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Full-Stack Developer - Angular Focus</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Imperial Health Holdings</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca22063859741953</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Business Intelligence (BI) Developer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26c52bf7b46f0d46</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>AEP Middleware Pod Kafka Admin</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, Kafka Connect, Snowflake, Oracle, Splunk, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c7915433a059ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9f54f4c0964669</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>DevOps Engineer III</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Victra-Verizon Authorized Retailer</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1bbd1ecd34ba576b</t>
         </is>

--- a/results/job_matches_2026-10-06.xlsx
+++ b/results/job_matches_2026-10-06.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,95 +456,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>KLS Martin Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>26.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71bf0245152c804d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d004bc892c60770</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer / BI Developer – GCP, dbt &amp; Power BI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OSI Digital</t>
+          <t>Nixon Web Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>25.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79eb3256392d49d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec453d2d16d9041</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Data - FreeWheel</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb9c7f9097d165</t>
+          <t>https://www.indeed.com/viewjob?jk=71bf0245152c804d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Commercial DT Senior Data Solution Developer</t>
+          <t>Data Engineer / BI Developer – GCP, dbt &amp; Power BI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>OSI Digital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec85fd3b937ce66</t>
+          <t>https://www.indeed.com/viewjob?jk=79eb3256392d49d1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. AI Cloud Platform Engineer</t>
+          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Scala, Power BI</t>
+          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,137 +624,137 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422f525072d1a9c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac0a80ae78e8a3b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Site Reliability Engineer, Data - FreeWheel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3904d0205e58da2c</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb9c7f9097d165</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Sr Software Engineer - Digital Banking</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lindfast Solutions Group</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=981d541cfbb05547</t>
+          <t>https://www.indeed.com/viewjob?jk=acb73e15b88b41b2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Ops / DevOps Engineer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meetic</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7952341ee0c6ac4</t>
+          <t>https://www.indeed.com/viewjob?jk=6415d34be34565d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,67 +764,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271ae7d8ee6706bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3904d0205e58da2c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Data Analyst - Agentic AI</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kroll Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819ad471f98483cc</t>
+          <t>https://www.indeed.com/viewjob?jk=78b96535deace3b6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956de72fea7773ed</t>
+          <t>https://www.indeed.com/viewjob?jk=271ae7d8ee6706bd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,34 +859,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f0317152441f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=956de72fea7773ed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Product Engineer, Karat Platform</t>
+          <t>Sr Engineer, IT Machine Learning</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,34 +894,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Scala, Oracle, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4503e534007dd850</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9e361c44f6f503</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,34 +929,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5425f278842298</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b7784fe0428d5f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer – Physical AI Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>MedVet</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,24 +974,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8048f9d73fd7da7</t>
+          <t>https://www.indeed.com/viewjob?jk=23bae3ccf06adcbd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer – Physical AI Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,34 +999,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Step Functions, SQS, SNS, BigQuery, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1d738eb2126f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a8048f9d73fd7da7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Sr. Database Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Integrated Financial Settlements</t>
+          <t>USA TODAY Co.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Kafka</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870e38fac0b2d478</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab3e0fa8a0586bd</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>iClassPro, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1069,34 +1069,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5b52e17a5bd63e</t>
+          <t>https://www.indeed.com/viewjob?jk=579a554b68cd573e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer-3</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Credit Union of Texas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,34 +1104,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33bb747e2908314c</t>
+          <t>https://www.indeed.com/viewjob?jk=933f7b241bea8b88</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Back-End Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>iClassPro, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,34 +1139,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=579a554b68cd573e</t>
+          <t>https://www.indeed.com/viewjob?jk=d422fc46951e5afd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. People Analytics Engineer</t>
+          <t>Cloud Engineer-API -Global Industrial</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,77 +1174,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92e55014f77298b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1626850211bd78e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Palomar College</t>
+          <t>Easterseals Southern California</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5c414e4ee4b328</t>
+          <t>https://www.indeed.com/viewjob?jk=07870ee9c10ac5c8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Triconn Solutions</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,59 +1254,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=985b7795e94b06ce</t>
+          <t>https://www.indeed.com/viewjob?jk=0b788dde189e4cc1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Back-End Developer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d422fc46951e5afd</t>
+          <t>https://www.indeed.com/viewjob?jk=099479d86490847b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Qbitech</t>
+          <t>Rooms To Go</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Seffner, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,34 +1314,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea14e8ca5424e9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=86f34931ade8cede</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect – GCP / Generative AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,34 +1349,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, ETL</t>
+          <t>AWS, Redshift, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b788dde189e4cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=26593bdfa803230a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Harris Computer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,34 +1384,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099479d86490847b</t>
+          <t>https://www.indeed.com/viewjob?jk=274f51e93c4990cb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Reliability Engineer I</t>
+          <t>Senior Software Engineer – Backend</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,34 +1419,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6dc0fbf3996a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff1e374638f96eca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Reliability Engineer I</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,34 +1454,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708e5d96e2689486</t>
+          <t>https://www.indeed.com/viewjob?jk=8db24154655e7b30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rooms To Go</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seffner, FL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,34 +1489,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f34931ade8cede</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0306b9c06d1ef3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,34 +1524,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e21d24f6967c76</t>
+          <t>https://www.indeed.com/viewjob?jk=02f1ae8db3b512b9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend</t>
+          <t>Digital Provider Software Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff1e374638f96eca</t>
+          <t>https://www.indeed.com/viewjob?jk=22b0f3b9859f414e</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db24154655e7b30</t>
+          <t>https://www.indeed.com/viewjob?jk=86a9ba9a98dcb9b2</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0306b9c06d1ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd6f7ce6a7a901</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f1ae8db3b512b9</t>
+          <t>https://www.indeed.com/viewjob?jk=87f1b7beb2c6b9c0</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b0f3b9859f414e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb96a18f22d94cfc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a9ba9a98dcb9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9109c01437b799</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd6f7ce6a7a901</t>
+          <t>https://www.indeed.com/viewjob?jk=0aef30d45a8f939e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Software Engineer - Advanced Analytics</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,42 +1804,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87f1b7beb2c6b9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=44ef5d52f3729890</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Spark, PySpark, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,102 +1849,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb96a18f22d94cfc</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c126f4e3cc33b7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Allied Benefit Systems</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9109c01437b799</t>
+          <t>https://www.indeed.com/viewjob?jk=2168430383941cce</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Digital Provider Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Solace Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, dbt, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aef30d45a8f939e</t>
+          <t>https://www.indeed.com/viewjob?jk=164a7939c0934d10</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer, Advanced Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,24 +1954,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ef5d52f3729890</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb80f8127789b70</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform &amp; DevSecOps Delivery Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>Harris Computer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,24 +1989,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c126f4e3cc33b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfe33f29178a80c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeler/Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Allied Benefit Systems</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,34 +2014,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2168430383941cce</t>
+          <t>https://www.indeed.com/viewjob?jk=502877bcd9cec430</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr AI/Data Science Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Solace Health</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,34 +2049,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, dbt, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164a7939c0934d10</t>
+          <t>https://www.indeed.com/viewjob?jk=96bdba5085886da3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>Azure, Databricks, GCP, Vertex AI, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb80f8127789b70</t>
+          <t>https://www.indeed.com/viewjob?jk=fbab632d0bb04999</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Modeler/Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=065b398cf1864aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=94f029f2695a0348</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f029f2695a0348</t>
+          <t>https://www.indeed.com/viewjob?jk=2532cb430ae39af4</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2532cb430ae39af4</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb45b4747cbece</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb45b4747cbece</t>
+          <t>https://www.indeed.com/viewjob?jk=6d991735fb9948be</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d991735fb9948be</t>
+          <t>https://www.indeed.com/viewjob?jk=3966f55aaa1e266e</t>
         </is>
       </c>
     </row>
@@ -2304,32 +2304,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3966f55aaa1e266e</t>
+          <t>https://www.indeed.com/viewjob?jk=710806077ea87813</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Full-stack Engineer 4 - Card Tech</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,67 +2339,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710806077ea87813</t>
+          <t>https://www.indeed.com/viewjob?jk=854d296ae3e1537f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Workday Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Yitro Global</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f01cb6ed116418a</t>
+          <t>https://www.indeed.com/viewjob?jk=498781f26e16eb5d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Advanced Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Vertex AI, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,32 +2409,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbab632d0bb04999</t>
+          <t>https://www.indeed.com/viewjob?jk=8ede594b070d17f3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,32 +2444,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe90612a7cd40771</t>
+          <t>https://www.indeed.com/viewjob?jk=f42ea61bfb332a47</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653ba6f45e27b32b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c44231ffe29ae48</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Card Tech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Converse, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854d296ae3e1537f</t>
+          <t>https://www.indeed.com/viewjob?jk=fadd1c9e9b39a370</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2549,24 +2549,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=498781f26e16eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb72e2bc4fddaba5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2574,34 +2574,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ede594b070d17f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d42345033b70a0ad</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Oracle Database Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,34 +2609,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42ea61bfb332a47</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ff4c841a1ca7d4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Erwin Data Modeler</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Tekcogno</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,34 +2644,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Hadoop, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c44231ffe29ae48</t>
+          <t>https://www.indeed.com/viewjob?jk=89810a7e8484847e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Converse, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,34 +2679,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadd1c9e9b39a370</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb03498bcaeb2d4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,34 +2714,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb72e2bc4fddaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=0020052b83f9ef57</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,34 +2749,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ff7692093a84ad</t>
+          <t>https://www.indeed.com/viewjob?jk=767b9e8e13621baf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer - Digital Marketing</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wilson Language Training Corp.</t>
+          <t>Live Oak Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,34 +2784,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=206b79ebbffc09e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4a3a03e231e77efd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Erwin Data Modeler</t>
+          <t>Full-stack Engineer 4, Cyber Endpoint Security</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tekcogno</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,34 +2819,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89810a7e8484847e</t>
+          <t>https://www.indeed.com/viewjob?jk=768daf548bf7f04f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Consultant, Full Stack API Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2864,24 +2864,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=769605ecbc4da595</t>
+          <t>https://www.indeed.com/viewjob?jk=727d755000763cf2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Digital Marketing</t>
+          <t>Full Stack Engineer 4 (ServiceNow)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Live Oak Bank</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,24 +2889,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a3a03e231e77efd</t>
+          <t>https://www.indeed.com/viewjob?jk=abe17e114c2bcc25</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Cyber Endpoint Security</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2934,14 +2934,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=768daf548bf7f04f</t>
+          <t>https://www.indeed.com/viewjob?jk=239112321618bfea</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727d755000763cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f20993d5ae69d49</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (ServiceNow)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe17e114c2bcc25</t>
+          <t>https://www.indeed.com/viewjob?jk=77827d49349dcffa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3039,32 +3039,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239112321618bfea</t>
+          <t>https://www.indeed.com/viewjob?jk=d562816e08aec62b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Python, AWS)</t>
+          <t>AI Software Engineer - Senior</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3074,32 +3074,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f20993d5ae69d49</t>
+          <t>https://www.indeed.com/viewjob?jk=2748f5c3e0997c3f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>AI Software Engineer - Senior</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3109,59 +3109,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77827d49349dcffa</t>
+          <t>https://www.indeed.com/viewjob?jk=b748bf2b91e4a02e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4</t>
+          <t>Senior Software Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d562816e08aec62b</t>
+          <t>https://www.indeed.com/viewjob?jk=b77e2e5fec6bdd9d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Senior</t>
+          <t>Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3169,34 +3169,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2748f5c3e0997c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4f2633f539c6b2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Senior</t>
+          <t>Sr. Fullstack Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3204,34 +3204,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, Talend, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b748bf2b91e4a02e</t>
+          <t>https://www.indeed.com/viewjob?jk=6372ad68f53bdf20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Automation Engineer</t>
+          <t>Backend Software Engineer, Weather &amp; Aviation</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>spire</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3239,34 +3239,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Scala, Python</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Kafka, Dask</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33a4e4327114b742</t>
+          <t>https://www.indeed.com/viewjob?jk=1555a6e30192df1d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Security Operations Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>bet365</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, MLOps, CI/CD, Terraform</t>
+          <t>RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3284,24 +3284,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e156aa015e45d8c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4f493bcc576c8206</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Engineer (1042) – Department of Technology</t>
+          <t>Full-Stack Developer - Angular Focus</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>Imperial Health Holdings</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3309,34 +3309,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe04b5d2de255308</t>
+          <t>https://www.indeed.com/viewjob?jk=ca22063859741953</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence (BI) Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shoals Technologies Group</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3354,24 +3354,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821c9233233a720b</t>
+          <t>https://www.indeed.com/viewjob?jk=26c52bf7b46f0d46</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3379,34 +3379,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35e334b90160652</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1901ef9cd7bdba</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Novacis Digital</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3414,34 +3414,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>IAM, Azure, Data Factory, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6372ad68f53bdf20</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb729860cdaaf66</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, Weather &amp; Aviation</t>
+          <t>Engineer III, Business Intelligence</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Spire Global</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Kafka, Dask</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20f49a9fd1e357a</t>
+          <t>https://www.indeed.com/viewjob?jk=a84d75c098494a33</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>spire</t>
+          <t>Spire Global</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3494,24 +3494,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555a6e30192df1d</t>
+          <t>https://www.indeed.com/viewjob?jk=b20f49a9fd1e357a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AEP Middleware Pod Kafka Admin</t>
+          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3519,34 +3519,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Kafka Connect, Snowflake, Oracle, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c7915433a059ea</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9f54f4c0964669</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Angular Focus</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Imperial Health Holdings</t>
+          <t>Victra-Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3554,34 +3554,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca22063859741953</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbd1ecd34ba576b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business Intelligence (BI) Developer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3589,87 +3589,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c52bf7b46f0d46</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9f54f4c0964669</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>DevOps Engineer III</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Victra-Verizon Authorized Retailer</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbd1ecd34ba576b</t>
+          <t>https://www.indeed.com/viewjob?jk=763cf004d1e71458</t>
         </is>
       </c>
     </row>
